--- a/data/source/bom_cronos_n04.xlsx
+++ b/data/source/bom_cronos_n04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,91 @@
           <t>critico</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>T41</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>T44</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>T45</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>T46</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>T47</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>T48</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>T49</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>T50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,21 +536,69 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cuero vacuno</t>
+          <t>Suela de poliuretano (PU)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.19</v>
+          <t>g</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
+      </c>
+      <c r="F2" t="n">
+        <v>369.167</v>
+      </c>
+      <c r="G2" t="n">
+        <v>369.167</v>
+      </c>
+      <c r="H2" t="n">
+        <v>379.167</v>
+      </c>
+      <c r="I2" t="n">
+        <v>379.167</v>
+      </c>
+      <c r="J2" t="n">
+        <v>417.167</v>
+      </c>
+      <c r="K2" t="n">
+        <v>433.167</v>
+      </c>
+      <c r="L2" t="n">
+        <v>449.167</v>
+      </c>
+      <c r="M2" t="n">
+        <v>479.167</v>
+      </c>
+      <c r="N2" t="n">
+        <v>483.167</v>
+      </c>
+      <c r="O2" t="n">
+        <v>533.167</v>
+      </c>
+      <c r="P2" t="n">
+        <v>509.167</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>563.167</v>
+      </c>
+      <c r="R2" t="n">
+        <v>563.167</v>
+      </c>
+      <c r="S2" t="n">
+        <v>587.167</v>
+      </c>
+      <c r="T2" t="n">
+        <v>587.167</v>
+      </c>
+      <c r="U2" t="n">
+        <v>587.167</v>
+      </c>
+      <c r="V2" t="n">
+        <v>587.167</v>
       </c>
     </row>
     <row r="3">
@@ -476,7 +609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Suela de poliuretano (PU)</t>
+          <t>Puntera de acero</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,12 +634,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puntera de acero</t>
+          <t>Caja de empaque</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>par</t>
+          <t>unidad</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -526,7 +659,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plantilla anatómica</t>
+          <t>Capellada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,7 +684,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cordones 120 cm</t>
+          <t>Plantilla armado</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,16 +709,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hilo de coser poliéster</t>
+          <t>Plantilla vista</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>par</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -601,16 +734,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ojalillos metálicos</t>
+          <t>Hilo de coser poliéster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unidad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -626,16 +759,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adhesivo de poliuretano</t>
+          <t>Cordones trenzados 0.90m</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>par</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -651,16 +784,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Forro interior textil</t>
+          <t>Tinta para PU (gris)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -676,18 +809,68 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Etiqueta y caja individual</t>
+          <t>Tinta para PU (negro)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INS-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Conjunto armado</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>unidad</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INS-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Flyer condiciones de uso</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
